--- a/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -379,228 +379,221 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:6">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="B1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="0" t="s">
+      <x:c r="D1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="0" t="s">
+      <x:c r="E1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="0" t="s">
+      <x:c r="F1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="0">
+      <x:c r="A2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
-      <x:c r="A3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
+      <x:c r="A3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="D4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F4" s="0">
+      <x:c r="F4">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
-      <x:c r="A5" s="0">
+      <x:c r="A5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F5" s="0">
+      <x:c r="F5">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
-      <x:c r="A6" s="0">
+      <x:c r="A6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E6" s="0">
+      <x:c r="E6">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F6" s="0">
+      <x:c r="F6">
         <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A2:A6">
     <x:cfRule type="dataBar" priority="1">
-      <x:dataBar showValue="1">
+      <x:dataBar>
         <x:cfvo type="min"/>
         <x:cfvo type="max"/>
         <x:color rgb="FFFFBF00"/>
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9c3d3c0-5f8c-4a6f-adb6-3635b1a2e329}</x14:id>
+          <x14:id>{923ccae3-bb83-46fe-8066-72841291b0e5}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="B2:B6">
     <x:cfRule type="dataBar" priority="2">
-      <x:dataBar showValue="1">
+      <x:dataBar>
         <x:cfvo type="min" val="0"/>
         <x:cfvo type="max" val="0"/>
         <x:color rgb="FF21ABCD"/>
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b62cf8c4-b196-42a2-9969-660980997667}</x14:id>
+          <x14:id>{bdd7f59a-fc33-45a6-ab8f-9442a0f0714e}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="C2:C6">
     <x:cfRule type="dataBar" priority="3">
-      <x:dataBar showValue="1">
+      <x:dataBar>
         <x:cfvo type="num" val="0"/>
         <x:cfvo type="num" val="10"/>
         <x:color rgb="FF536872"/>
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a8f8f7a-a6c2-4b35-9264-856c9ed096dc}</x14:id>
+          <x14:id>{1dbcec3f-1904-44be-b805-20e249e7db46}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="D2:D6">
     <x:cfRule type="dataBar" priority="4">
-      <x:dataBar showValue="1">
+      <x:dataBar>
         <x:cfvo type="percent" val="50"/>
         <x:cfvo type="percent" val="100"/>
         <x:color rgb="FFC19A6B"/>
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e63efefd-de5a-4b56-8e84-9ab2469077cd}</x14:id>
+          <x14:id>{e56ec669-a7bf-4943-9226-423503f6f826}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E2:E6">
     <x:cfRule type="dataBar" priority="5">
-      <x:dataBar showValue="1">
+      <x:dataBar>
         <x:cfvo type="formula" val="-SUM($A$2:$E$2)"/>
         <x:cfvo type="formula" val="SUM($A$6:$E$6)"/>
         <x:color rgb="FFC2B280"/>
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3103f3ec-bcf3-4f5e-9ce6-034fe91a8a23}</x14:id>
+          <x14:id>{efebc32e-22e2-4124-a43e-992b7a3ede75}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F2:F6">
     <x:cfRule type="dataBar" priority="6">
-      <x:dataBar showValue="1">
+      <x:dataBar>
         <x:cfvo type="percentile" val="30"/>
         <x:cfvo type="percentile" val="70"/>
         <x:color rgb="FFB53389"/>
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c71b0ff-5a12-4137-9871-cb858ec8b916}</x14:id>
+          <x14:id>{3962cb80-2ea0-467c-8f32-b8101f1c93ef}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f9c3d3c0-5f8c-4a6f-adb6-3635b1a2e329}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+          <x14:cfRule type="dataBar" id="{923ccae3-bb83-46fe-8066-72841291b0e5}">
+            <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
               <x14:negativeFillColor rgb="FFFFBF00"/>
@@ -610,8 +603,8 @@
           <xm:sqref>A2:A6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b62cf8c4-b196-42a2-9969-660980997667}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+          <x14:cfRule type="dataBar" id="{bdd7f59a-fc33-45a6-ab8f-9442a0f0714e}">
+            <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
               </x14:cfvo>
@@ -625,8 +618,8 @@
           <xm:sqref>B2:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3a8f8f7a-a6c2-4b35-9264-856c9ed096dc}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+          <x14:cfRule type="dataBar" id="{1dbcec3f-1904-44be-b805-20e249e7db46}">
+            <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
               </x14:cfvo>
@@ -640,8 +633,8 @@
           <xm:sqref>C2:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e63efefd-de5a-4b56-8e84-9ab2469077cd}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+          <x14:cfRule type="dataBar" id="{e56ec669-a7bf-4943-9226-423503f6f826}">
+            <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>50</xm:f>
               </x14:cfvo>
@@ -655,8 +648,8 @@
           <xm:sqref>D2:D6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3103f3ec-bcf3-4f5e-9ce6-034fe91a8a23}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+          <x14:cfRule type="dataBar" id="{efebc32e-22e2-4124-a43e-992b7a3ede75}">
+            <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>-SUM($A$2:$E$2)</xm:f>
               </x14:cfvo>
@@ -670,8 +663,8 @@
           <xm:sqref>E2:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8c71b0ff-5a12-4137-9871-cb858ec8b916}">
-            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+          <x14:cfRule type="dataBar" id="{3962cb80-2ea0-467c-8f32-b8101f1c93ef}">
+            <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>30</xm:f>
               </x14:cfvo>
